--- a/AjoutOngletRessources/ig/all-profiles.xlsx
+++ b/AjoutOngletRessources/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T08:10:06+00:00</t>
+    <t>2024-07-26T09:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AjoutOngletRessources/ig/all-profiles.xlsx
+++ b/AjoutOngletRessources/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-26T09:18:38+00:00</t>
+    <t>2024-07-30T13:59:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AjoutOngletRessources/ig/all-profiles.xlsx
+++ b/AjoutOngletRessources/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-30T13:59:27+00:00</t>
+    <t>2024-07-30T14:16:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
